--- a/doc/samples/sample-application-reviewed.xlsx
+++ b/doc/samples/sample-application-reviewed.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>判断に必要な情報を確認してください。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
+          <t>(デモ) retrieval ヒット=False</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -568,12 +568,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>判断に必要な情報を確認してください。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
+          <t>(デモ) retrieval ヒット=False</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -606,23 +606,27 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>許可</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>参考情報に照らし問題は認められません。</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>(デモ) retrieval ヒット=True</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>データ保管リージョン / データレジデンシー; バックアップ（3-2-1 ルール）</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -649,23 +653,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>許可</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>参考情報に照らし問題は認められません。</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>(デモ) retrieval ヒット=True</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>保管データの暗号化（AWS）; データ保管リージョン / データレジデンシー</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -692,23 +700,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>許可</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>参考情報に照らし問題は認められません。</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>(デモ) retrieval ヒット=True</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>アクセス制御 / 多要素認証</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -735,23 +747,27 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>許可</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>参考情報に照らし問題は認められません。</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>(デモ) retrieval ヒット=True</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>監査ログ（CloudTrail / アクセスログ）; データ保管リージョン / データレジデンシー</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -778,23 +794,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>許可</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>参考情報に照らし問題は認められません。</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>(デモ) retrieval ヒット=True</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>バックアップ（3-2-1 ルール）; データ保管リージョン / データレジデンシー</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -826,12 +846,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>（C3 で RAG + Bedrock により返答案を生成）</t>
+          <t>判断に必要な情報を確認してください。</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>C2 スタブ: Excel 入出力の往復確認用。判定ロジックは C3 で実装。</t>
+          <t>(デモ) retrieval ヒット=False</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
